--- a/BWI/bestwine_output/bestwine_Costa Rica.xlsx
+++ b/BWI/bestwine_output/bestwine_Costa Rica.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA75"/>
+  <dimension ref="A1:AA76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8460,6 +8460,83 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>La Napoli Bajureña S.a.</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>La Napoli Bajureña S.a.</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>122575</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Comunidad</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Guanacaste</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Centro Comercial Do It Center</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>50502</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://discostarica.com</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>pedidos.disguardia@gmail.com</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>+506 2667 1201</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/discostarica/</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr"/>
+      <c r="X76" s="2" t="inlineStr"/>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Costa Rica.xlsx
+++ b/BWI/bestwine_output/bestwine_Costa Rica.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA76"/>
+  <dimension ref="A1:AA77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8537,6 +8537,83 @@
       <c r="Z76" s="2" t="inlineStr"/>
       <c r="AA76" s="2" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>La Napoli Bajureña S.a.</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>La Napoli Bajureña S.a.</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>122575</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Comunidad</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Provincia de Guanacaste</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Centro Comercial Do It Center</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>50502</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://discostarica.com</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>pedidos.disguardia@gmail.com</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>+506 2667 1201</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/discostarica/</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr"/>
+      <c r="X77" s="2" t="inlineStr"/>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
